--- a/data/trans_bre/P1409-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1409-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,25</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,99</t>
+          <t>-0,98; 1,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,11</t>
+          <t>-0,24; 3,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,05</t>
+          <t>-0,9; 3,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 113,28</t>
+          <t>-29,28; 92,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 135,46</t>
+          <t>-7,85; 142,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 79,05</t>
+          <t>-14,81; 92,9</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>109,04%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,59</t>
+          <t>-0,15; 1,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,54</t>
+          <t>0,21; 2,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 13,57</t>
+          <t>-0,46; 2,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 123,05</t>
+          <t>-7,98; 146,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 123,57</t>
+          <t>6,32; 122,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 453,73</t>
+          <t>-11,1; 75,02</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,15</t>
+          <t>-1,0; 3,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,88</t>
+          <t>-0,25; 3,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,09</t>
+          <t>-2,13; 2,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 338,68</t>
+          <t>-46,4; 351,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 373,39</t>
+          <t>-16,72; 439,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,72; 80,15</t>
+          <t>-36,88; 96,29</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,5</t>
+          <t>0,08; 1,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,27</t>
+          <t>0,6; 2,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 8,79</t>
+          <t>-0,16; 1,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 92,79</t>
+          <t>2,25; 96,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,57; 102,15</t>
+          <t>19,61; 108,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,98; 289,34</t>
+          <t>-3,9; 55,2</t>
         </is>
       </c>
     </row>
